--- a/data/output/West_Market_Summary.xlsx
+++ b/data/output/West_Market_Summary.xlsx
@@ -415,14 +415,6 @@
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
